--- a/artfynd/A 43161-2022 artfynd.xlsx
+++ b/artfynd/A 43161-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43161-2022 artfynd.xlsx
+++ b/artfynd/A 43161-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80675662</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547227.8795091176</v>
+        <v>547228</v>
       </c>
       <c r="R2" t="n">
-        <v>7111178.202218422</v>
+        <v>7111178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>80675663</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547160.896298178</v>
+        <v>547161</v>
       </c>
       <c r="R3" t="n">
-        <v>7111209.953039608</v>
+        <v>7111210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,12 +890,7 @@
         <v>80675664</v>
       </c>
       <c r="B4" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547091.2105146663</v>
+        <v>547091</v>
       </c>
       <c r="R4" t="n">
-        <v>7111246.907060249</v>
+        <v>7111247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +959,9 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43161-2022 artfynd.xlsx
+++ b/artfynd/A 43161-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,8 +1001,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>